--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/5371-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/5371-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{30C4E8CD-F591-4A29-9F28-1367AB4DDC6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F47E3ED1-EEC7-497B-892D-85F10C1C2417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{2807AB2C-249F-4261-9833-6C7DE80255E3}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{D4B23548-716A-46D2-9675-9056F96142F3}"/>
   </bookViews>
   <sheets>
     <sheet name="5371-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1487,29 +1487,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74E8DA43-ED87-4C1D-875B-F63EF53C8681}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{367F79D2-24D1-4463-8EF4-3FE8639BFFA4}">
   <dimension ref="A1:X38"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1543,7 +1542,7 @@
       <c r="W1" s="27"/>
       <c r="X1" s="19"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1579,7 +1578,7 @@
       <c r="W2" s="29"/>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1631,7 +1630,7 @@
       </c>
       <c r="X3" s="33"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1699,7 +1698,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>2024</v>
       </c>
@@ -1771,7 +1770,7 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="36">
         <v>2023</v>
       </c>
@@ -1843,7 +1842,7 @@
         <v>4.93</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>2022</v>
       </c>
@@ -1915,7 +1914,7 @@
         <v>8.09</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="36">
         <v>2021</v>
       </c>
@@ -1987,7 +1986,7 @@
         <v>8.59</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>2020</v>
       </c>
@@ -2059,7 +2058,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2019</v>
       </c>
@@ -2131,7 +2130,7 @@
         <v>7.56</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>2018</v>
       </c>
@@ -2203,7 +2202,7 @@
         <v>9.43</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2017</v>
       </c>
@@ -2275,7 +2274,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>2016</v>
       </c>
@@ -2347,7 +2346,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>2015</v>
       </c>
@@ -2419,7 +2418,7 @@
         <v>6.02</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>2014</v>
       </c>
@@ -2491,7 +2490,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2013</v>
       </c>
@@ -2563,7 +2562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="34">
         <v>2012</v>
       </c>
@@ -2635,7 +2634,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>2011</v>
       </c>
@@ -2707,7 +2706,7 @@
         <v>8.7200000000000006</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="34">
         <v>2010</v>
       </c>
@@ -2779,7 +2778,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>2009</v>
       </c>
@@ -2851,7 +2850,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="34">
         <v>2008</v>
       </c>
@@ -2923,7 +2922,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>2007</v>
       </c>
@@ -2995,7 +2994,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="34">
         <v>2006</v>
       </c>
@@ -3067,7 +3066,7 @@
         <v>9.59</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>2005</v>
       </c>
@@ -3139,7 +3138,7 @@
         <v>6.22</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="34">
         <v>2004</v>
       </c>
@@ -3211,7 +3210,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>2003</v>
       </c>
@@ -3283,7 +3282,7 @@
         <v>6.18</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="34">
         <v>2002</v>
       </c>
@@ -3355,7 +3354,7 @@
         <v>9.57</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2001</v>
       </c>
@@ -3427,7 +3426,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="34">
         <v>2000</v>
       </c>
@@ -3499,7 +3498,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>1999</v>
       </c>
@@ -3571,7 +3570,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="34">
         <v>1998</v>
       </c>
@@ -3643,7 +3642,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <v>1997</v>
       </c>
@@ -3715,7 +3714,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="34">
         <v>1996</v>
       </c>
@@ -3787,7 +3786,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="36">
         <v>1995</v>
       </c>
@@ -3859,7 +3858,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="34">
         <v>1994</v>
       </c>
@@ -3931,7 +3930,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="36">
         <v>1993</v>
       </c>
@@ -4003,7 +4002,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="34">
         <v>1992</v>
       </c>
@@ -4075,7 +4074,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="36" t="s">
         <v>54</v>
       </c>
